--- a/src/main/resources/client-labels/apc-etiquetas-japan.xlsx
+++ b/src/main/resources/client-labels/apc-etiquetas-japan.xlsx
@@ -3,19 +3,23 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\documentos\ETIQUETAS\APC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\system.PUNTOTRES\Documents\WORKSPACE\PackingListAutomation\target\muestras-etiquetas-apc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C799E001-FA4A-44F0-80F7-A69578131C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE906837-12AE-476B-B8CF-A664215CE032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="857" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="857" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Etiquette colis Bolloré " sheetId="3" r:id="rId1"/>
     <sheet name="Etiquette Palette Bolloré" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Etiquette colis Bolloré '!$A$1:$D$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Etiquette Palette Bolloré'!$A$1:$D$26</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="35">
   <si>
     <r>
       <t xml:space="preserve">SERVICE Bolloré Logistics ROISSY                             </t>
@@ -228,22 +232,57 @@
     <t>U</t>
   </si>
   <si>
-    <t>PUN20260717JPT1</t>
-  </si>
-  <si>
     <t>PXCBC-F67008</t>
   </si>
   <si>
-    <t>KAN-TILLEUL</t>
-  </si>
-  <si>
     <t>7,60 Kg</t>
   </si>
   <si>
-    <t>9 / 9</t>
-  </si>
-  <si>
-    <t>64,58 Kg</t>
+    <t>EXPEDITEUR
+(Shipper / Sender)
+-
+PROVENANCE
+(Origin)</t>
+  </si>
+  <si>
+    <t>DESTINATAIRE
+(Consignee)</t>
+  </si>
+  <si>
+    <t>DESTINATION
+(Destination)</t>
+  </si>
+  <si>
+    <t>4100128863</t>
+  </si>
+  <si>
+    <t>PUN20260928WH1</t>
+  </si>
+  <si>
+    <t>LZZ-NOIR</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>1 / 3</t>
+  </si>
+  <si>
+    <t>SERVICE Bolloré Logistics ROISSY (Bolloré Logistics Roissy Department)</t>
+  </si>
+  <si>
+    <t>Nombre total de colis sur la palette
+(Total number of packages on the palette)</t>
+  </si>
+  <si>
+    <t>Poids brut 
+(Total gross weight)</t>
+  </si>
+  <si>
+    <t>25,20 Kg</t>
+  </si>
+  <si>
+    <t>16,20 Kg</t>
   </si>
 </sst>
 </file>
@@ -509,15 +548,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>3190874</xdr:colOff>
+      <xdr:colOff>3225511</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>105641</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>903816</xdr:colOff>
+      <xdr:colOff>938453</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>105641</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -547,8 +586,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3505199" y="19050"/>
-          <a:ext cx="1761067" cy="762000"/>
+          <a:off x="3623829" y="105641"/>
+          <a:ext cx="1765397" cy="762000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -583,15 +622,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>3190874</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>3225511</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>17318</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>903816</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>938453</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>36368</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -621,8 +660,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="11994695" y="19050"/>
-          <a:ext cx="1767871" cy="762000"/>
+          <a:off x="3623829" y="8814954"/>
+          <a:ext cx="1765397" cy="590550"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -664,13 +703,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>3190874</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>903816</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -700,8 +739,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3467099" y="19050"/>
-          <a:ext cx="1761067" cy="762000"/>
+          <a:off x="3889374" y="368300"/>
+          <a:ext cx="1554692" cy="762000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -729,6 +768,50 @@
             </a14:hiddenLine>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3206749</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>919691</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3905249" y="7480300"/>
+          <a:ext cx="1554692" cy="762000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1027,219 +1110,189 @@
     <tabColor theme="6" tint="0.39997558519241921"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B6:C40"/>
+  <dimension ref="B5:C36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="1"/>
-    <col min="2" max="3" width="60.7109375" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.85546875"/>
+    <col min="2" max="3" customWidth="true" width="60.7109375"/>
+    <col min="4" max="4" customWidth="true" width="5.85546875"/>
   </cols>
   <sheetData>
-    <row r="6" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="2:3" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="4" t="s">
+    <row r="5" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="2:3" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="102" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="C7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" ht="102" thickBot="1" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="9" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="12"/>
+    </row>
     <row r="10" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="12">
-        <v>4100128683</v>
-      </c>
+      <c r="B10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="13"/>
     </row>
     <row r="11" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>20</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C11" s="13"/>
     </row>
     <row r="12" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>21</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C12" s="13"/>
     </row>
     <row r="13" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="8" t="s">
+      <c r="C13" s="13"/>
+    </row>
+    <row r="14" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="5" t="s">
+      <c r="C14" s="14"/>
+    </row>
+    <row r="15" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C15" s="15" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="2"/>
-      <c r="C17" s="16"/>
+    <row r="16" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="2"/>
+      <c r="C16" s="16"/>
+    </row>
+    <row r="17" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="17"/>
     </row>
     <row r="18" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="18"/>
+    </row>
+    <row r="19" spans="2:3" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="2:3" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" ht="102" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B27" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="12"/>
+    </row>
+    <row r="28" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B28" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="13"/>
+    </row>
+    <row r="29" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B29" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="13"/>
+    </row>
+    <row r="30" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="13"/>
+    </row>
+    <row r="31" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="13"/>
+    </row>
+    <row r="32" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="14"/>
+    </row>
+    <row r="33" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B34" s="2"/>
+      <c r="C34" s="16"/>
+    </row>
+    <row r="35" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="9" t="s">
+      <c r="C35" s="17"/>
+    </row>
+    <row r="36" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="2:3" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" ht="102" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B31" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="12">
-        <v>4100128683</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B32" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B33" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B34" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B35" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="2"/>
-      <c r="C38" s="16"/>
-    </row>
-    <row r="39" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>23</v>
-      </c>
+      <c r="C36" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="61" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="62" fitToWidth="0" orientation="portrait" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -1248,81 +1301,75 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="6" tint="0.39997558519241921"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:E14"/>
+  <dimension ref="B4:C13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.140625" customWidth="1"/>
-    <col min="2" max="3" width="57.5703125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="10.42578125"/>
+    <col min="2" max="3" customWidth="true" width="57.5703125"/>
+    <col min="4" max="4" customWidth="true" width="10.42578125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="E1">
+    <row r="4" spans="2:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+    </row>
+    <row r="5" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="2:3" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="102" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-    </row>
-    <row r="7" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="2:5" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="102" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="2"/>
-    </row>
-    <row r="13" spans="2:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="10" t="s">
+    <row r="10" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11" spans="2:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="11" t="s">
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="2:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="2:3" ht="52.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B6:C6"/>
+  <mergeCells count="2">
+    <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="0.31496062992125984" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="95" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="72" fitToWidth="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>